--- a/docs/legal/retention-verification-schedule.xlsx
+++ b/docs/legal/retention-verification-schedule.xlsx
@@ -1506,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1645,27 +1645,27 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>auth_challenge.ip</t>
+          <t>login_trusted_ip.ip_hash</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Pre-session MFA challenge (5-minute life)</t>
+          <t>Login throttling: IPs that previously succeeded for the account (SHA-256 hash)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>NO - stored regardless of the switch</t>
+          <t>NO - not governed by the switch</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>AUTH_TRANSIENT; row not purged today</t>
+          <t>AUTH_TRANSIENT category by analogy; kept per user with no expiry today</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Is the IP needed at all on a challenge that lives five minutes?</t>
+          <t>A hashed IP is still personal data (pseudonymised). Is indefinite retention justified, or should entries expire?</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
@@ -1674,27 +1674,27 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>login_trusted_ip.ip_hash</t>
+          <t>Redis login-throttle keys (lt:ip, lt:pair, lt:acct: SHA-256 hashes of IP and e-mail, truncated)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Login throttling: IPs that previously succeeded for the account (SHA-256 hash)</t>
+          <t>Brute-force protection</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>NO - not governed by the switch</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>AUTH_TRANSIENT category by analogy; kept per user with no expiry today</t>
+          <t>Keys expire within minutes (TTL about 15 minutes; verified in code and test)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>A hashed IP is still personal data (pseudonymised). Is indefinite retention justified, or should entries expire?</t>
+          <t>Probably fine; confirm that short-lived hashed keys need no further treatment.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
@@ -1703,12 +1703,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Redis throttling keys (lt:ip, lt:pair, lt:acct: hashes of IP and e-mail)</t>
+          <t>Redis rate-limit keys (rl:&lt;route&gt;:ip:&lt;IP&gt; and rl:mfa:ip:&lt;IP&gt; - the RAW IP address in the key name; added by the DEC-013 investigation, correcting an earlier statement that all Redis keys were hashed)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Brute-force protection</t>
+          <t>Per-IP request rate limiting on authentication routes</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1718,16 +1718,45 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Keys expire within minutes (TTL about 15 minutes; verified in code)</t>
+          <t>Keys expire after their window (seconds to one hour; verified by test)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Probably fine; confirm that short-lived hashed keys need no further treatment.</t>
+          <t>Raw IPs in Redis for up to an hour: acceptable for rate limiting, or should the key be hashed like the login-throttle keys? Redis persistence/backup settings are an input.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>auth_challenge.ip - written at the password step when MFA is required; NEVER READ by any code (found by the DEC-013 investigation)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>None found in the code: collection without a use</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Row not purged</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Data-minimisation question: stop collecting it? (A proposal, not a change.)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
